--- a/templates/intake/promotions.xlsx
+++ b/templates/intake/promotions.xlsx
@@ -546,10 +546,10 @@
         </is>
       </c>
       <c r="D2" s="3" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>46323</v>
+        <v>46324</v>
       </c>
     </row>
     <row r="3">
